--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/StringFunctions.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/StringFunctions.xlsx
@@ -1583,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I58"/>
+  <dimension ref="A2:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1602,7 +1602,7 @@
     <row r="4" ht="43.5" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>An empty cell passes null. The checks treat null as an empty text: contains, startsWith, endsWith and isNumeric are false, isEmpty is true and length is 0. The functions that change a text return null for null. A null search text is never found, and a null text to remove or to search for leaves the text as it is.</t>
+          <t>An empty cell passes null. The checks treat null as an empty text: contains, startsWith, endsWith and isNumeric are false, isEmpty is true, length is 0, and like matches it with an empty pattern or *. The functions that change a text return null for null. A null search text is never found, and a null text to remove or to search for leaves the text as it is.</t>
         </is>
       </c>
     </row>
@@ -1689,296 +1689,287 @@
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>IsEmpty</t>
+          <t>Like</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>= isEmpty(text)</t>
+          <t>= like(text, "*")</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>IsNotEmpty</t>
+          <t>LikeEmptyPattern</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>= isNotEmpty(text)</t>
+          <t>= like(text, "")</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>IsNumeric</t>
+          <t>IsEmpty</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>= isNumeric(text)</t>
+          <t>= isEmpty(text)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>IsNotEmpty</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>= length(text)</t>
+          <t>= isNotEmpty(text)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>IsNumeric</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>= lowerCase(text)</t>
+          <t>= isNumeric(text)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>= upperCase(text)</t>
+          <t>= length(text)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Trim</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>= trim(text)</t>
+          <t>= lowerCase(text)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>= replace(text, "a", "b")</t>
+          <t>= upperCase(text)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>RemoveStart</t>
+          <t>Trim</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>= removeStart(text, "a")</t>
+          <t>= trim(text)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>RemoveEnd</t>
+          <t>Replace</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>= removeEnd(text, "a")</t>
+          <t>= replace(text, "a", "b")</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Substring</t>
+          <t>RemoveStart</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>= substring(text, 1)</t>
+          <t>= removeStart(text, "a")</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Substr</t>
+          <t>RemoveEnd</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>= substr(text, 1, 2)</t>
+          <t>= removeEnd(text, "a")</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Concatenate</t>
+          <t>Substring</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>= concatenate(text)</t>
+          <t>= substring(text, 1)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TextSplit</t>
+          <t>Substr</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>= textSplit(",", text)</t>
+          <t>= substr(text, 1, 2)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>ToInteger</t>
+          <t>Concatenate</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>= toInteger(text)</t>
+          <t>= concatenate(text)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>SearchNull</t>
+          <t>TextSplit</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>= contains("OpenL", text)</t>
+          <t>= textSplit(",", text)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>PrefixNull</t>
+          <t>ToInteger</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>= startsWith("OpenL", text)</t>
+          <t>= toInteger(text)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>RemoveNull</t>
+          <t>SearchNull</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>= removeStart("OpenL", text)</t>
+          <t>= contains("OpenL", text)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
+          <t>PrefixNull</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>= startsWith("OpenL", text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>RemoveNull</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>= removeStart("OpenL", text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
           <t>ReplaceNull</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>= replace("OpenL", text, "x")</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Test NullTexts NullTextsTest</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$Contains</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>contains(text, "x")</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ContainsChar</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>contains(text, 'x')</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ContainsAny</t>
+          <t>_res_.$Contains</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>containsAny(text, "xyz")</t>
+          <t>contains(text, "x")</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1990,12 +1981,12 @@
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>_res_.$StartsWith</t>
+          <t>_res_.$ContainsChar</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>startsWith(text, "x")</t>
+          <t>contains(text, 'x')</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -2007,12 +1998,12 @@
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>_res_.$EndsWith</t>
+          <t>_res_.$ContainsAny</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>endsWith(text, "x")</t>
+          <t>containsAny(text, "xyz")</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -2024,29 +2015,29 @@
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>_res_.$IsEmpty</t>
+          <t>_res_.$StartsWith</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>isEmpty(text)</t>
+          <t>startsWith(text, "x")</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>_res_.$IsNotEmpty</t>
+          <t>_res_.$EndsWith</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>isNotEmpty(text)</t>
+          <t>endsWith(text, "x")</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -2058,96 +2049,112 @@
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>_res_.$IsNumeric</t>
+          <t>_res_.$Like</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>isNumeric(text)</t>
+          <t>like(text, "*")</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Length</t>
+          <t>_res_.$LikeEmptyPattern</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>length(text)</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>0</v>
+          <t>like(text, "")</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Lower</t>
+          <t>_res_.$IsEmpty</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>lowerCase(text)</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="n"/>
+          <t>isEmpty(text)</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Upper</t>
+          <t>_res_.$IsNotEmpty</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>upperCase(text)</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n"/>
+          <t>isNotEmpty(text)</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Trim</t>
+          <t>_res_.$IsNumeric</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>trim(text)</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="n"/>
+          <t>isNumeric(text)</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Replace</t>
+          <t>_res_.$Length</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>replace(text, "a", "b")</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="n"/>
+          <t>length(text)</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>_res_.$RemoveStart</t>
+          <t>_res_.$Lower</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>removeStart(text, "a")</t>
+          <t>lowerCase(text)</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -2155,12 +2162,12 @@
     <row r="49">
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>_res_.$RemoveEnd</t>
+          <t>_res_.$Upper</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>removeEnd(text, "a")</t>
+          <t>upperCase(text)</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -2168,12 +2175,12 @@
     <row r="50">
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Substring</t>
+          <t>_res_.$Trim</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>substring(text, 1)</t>
+          <t>trim(text)</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -2181,12 +2188,12 @@
     <row r="51">
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Substr</t>
+          <t>_res_.$Replace</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>substr(text, 1, 2)</t>
+          <t>replace(text, "a", "b")</t>
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
@@ -2194,12 +2201,12 @@
     <row r="52">
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Concatenate</t>
+          <t>_res_.$RemoveStart</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>concatenate(text)</t>
+          <t>removeStart(text, "a")</t>
         </is>
       </c>
       <c r="D52" s="10" t="n"/>
@@ -2207,12 +2214,12 @@
     <row r="53">
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplit</t>
+          <t>_res_.$RemoveEnd</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>textSplit(",", text)</t>
+          <t>removeEnd(text, "a")</t>
         </is>
       </c>
       <c r="D53" s="10" t="n"/>
@@ -2220,12 +2227,12 @@
     <row r="54">
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ToInteger</t>
+          <t>_res_.$Substring</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>toInteger(text)</t>
+          <t>substring(text, 1)</t>
         </is>
       </c>
       <c r="D54" s="10" t="n"/>
@@ -2233,66 +2240,118 @@
     <row r="55">
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>_res_.$SearchNull</t>
+          <t>_res_.$Substr</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>contains("OpenL", text)</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>substr(text, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>_res_.$PrefixNull</t>
+          <t>_res_.$Concatenate</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>startsWith("OpenL", text)</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>concatenate(text)</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>_res_.$RemoveNull</t>
+          <t>_res_.$TextSplit</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>removeStart("OpenL", text)</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>OpenL</t>
-        </is>
-      </c>
+          <t>textSplit(",", text)</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="9" t="inlineStr">
         <is>
+          <t>_res_.$ToInteger</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>toInteger(text)</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$SearchNull</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>contains("OpenL", text)</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$PrefixNull</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>startsWith("OpenL", text)</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$RemoveNull</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>removeStart("OpenL", text)</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>OpenL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="9" t="inlineStr">
+        <is>
           <t>_res_.$ReplaceNull</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>replace("OpenL", text, "x")</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>OpenL</t>
         </is>
@@ -2300,8 +2359,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2315,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I74"/>
+  <dimension ref="A2:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2334,7 +2393,7 @@
     <row r="4" ht="43.5" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>like(text, pattern) checks the whole text against a pattern: ? is any character, * any number of characters, # a digit, @ a letter, [a-k] a character from a set, [!a-k] a character outside it, and "+" after a wildcard or a set repeats it once or more. [?], [*], [#], [@] and [+] match the characters themselves.</t>
+          <t>like(text, pattern) checks the whole text against a pattern: ? is any character, * any number of characters, # a digit, @ a letter of any alphabet, [a-k] a character from a set, [!a-k] a character outside it, and "+" after a wildcard or a set repeats it once or more. [?], [*], [#], [@] and [+] match the characters themselves.</t>
         </is>
       </c>
     </row>
@@ -2445,103 +2504,94 @@
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>NotInSet</t>
+          <t>LettersOfAnyAlphabet</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>= like("u", "[!v-z]")</t>
+          <t>= like("Øre", "@@@")</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Repeated</t>
+          <t>WordOfAnyAlphabet</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>= like("abc123", "@+#+")</t>
+          <t>= like("Мова", "@+")</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>RepeatedLetter</t>
+          <t>NotInSet</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>= like("aaa", "[a]+")</t>
+          <t>= like("u", "[!v-z]")</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>= like("abc123", "@+#+")</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>RepeatedLetter</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>= like("aaa", "[a]+")</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>LiteralQuestion</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>= like("a?", "a[?]")</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Test LikeExamples LikeExamplesTest</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$Phone</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>like("(29)687-11-53", "(##)###-##-##")</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$ShortPhone</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>like("(29)87-11-53", "(##)###-##-##")</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>_res_.$CodeInSet</t>
+          <t>_res_.$Phone</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>like("D1010", "[A-D]####")</t>
+          <t>like("(29)687-11-53", "(##)###-##-##")</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -2553,12 +2603,12 @@
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>_res_.$CodeOutOfSet</t>
+          <t>_res_.$ShortPhone</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>like("F1010", "[A-D]####")</t>
+          <t>like("(29)87-11-53", "(##)###-##-##")</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -2570,12 +2620,12 @@
     <row r="25">
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>_res_.$AnyCharacter</t>
+          <t>_res_.$CodeInSet</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>like("abc", "a?c")</t>
+          <t>like("D1010", "[A-D]####")</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -2587,29 +2637,29 @@
     <row r="26">
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>_res_.$AnyCharacters</t>
+          <t>_res_.$CodeOutOfSet</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>like("abbbc", "a*c")</t>
+          <t>like("F1010", "[A-D]####")</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>_res_.$LetterDigit</t>
+          <t>_res_.$AnyCharacter</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>like("x1", "@#")</t>
+          <t>like("abc", "a?c")</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -2621,12 +2671,12 @@
     <row r="28">
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>_res_.$NotInSet</t>
+          <t>_res_.$AnyCharacters</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>like("u", "[!v-z]")</t>
+          <t>like("abbbc", "a*c")</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -2638,12 +2688,12 @@
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Repeated</t>
+          <t>_res_.$LetterDigit</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>like("abc123", "@+#+")</t>
+          <t>like("x1", "@#")</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -2655,12 +2705,12 @@
     <row r="30">
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>_res_.$RepeatedLetter</t>
+          <t>_res_.$LettersOfAnyAlphabet</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>like("aaa", "[a]+")</t>
+          <t>like("Øre", "@@@")</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -2672,400 +2722,393 @@
     <row r="31">
       <c r="B31" s="9" t="inlineStr">
         <is>
+          <t>_res_.$WordOfAnyAlphabet</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>like("Мова", "@+")</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$NotInSet</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>like("u", "[!v-z]")</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Repeated</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>like("abc123", "@+#+")</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$RepeatedLetter</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>like("aaa", "[a]+")</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
           <t>_res_.$LiteralQuestion</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>like("a?", "a[?]")</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="43.5" customHeight="1">
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>The match is case-sensitive and covers the whole text: ? is exactly one character. An empty text matches only an empty pattern. Inside brackets, "!" right after "[" negates the set, but [!] alone is the "!" character, and a "-" at the start of a set is the "-" character. "+" after a plain character is that character itself. A space in the pattern matches one or more spaces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="36"/>
+    <row r="37" ht="43.5" customHeight="1">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>The match is case-sensitive and covers the whole text: ? is exactly one character. An empty text matches a pattern that needs no characters, such as an empty pattern or *. Inside brackets, "!" right after "[" negates the set, but [!] alone is the "!" character, and a "-" at the start of a set is the "-" character. "+" after a plain character is that character itself. A space in the pattern matches one or more spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Spreadsheet SpreadsheetResult LikeEdges()</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
+      <c r="C39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>OtherCase</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>= like("F", "f")</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>OneCharacterOnly</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>= like("abc", "?")</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>EmptyBoth</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>= like("", "")</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>EmptyPattern</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>= like("F", "")</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>EmptyText</t>
+          <t>OtherCase</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>= like("", "F")</t>
+          <t>= like("F", "f")</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>SetWithHyphen</t>
+          <t>OneCharacterOnly</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>= like("5-5", "[1-5][-4-6][5-9]")</t>
+          <t>= like("abc", "?")</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Exclamation</t>
+          <t>EmptyBoth</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>= like("!", "[!]")</t>
+          <t>= like("", "")</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>NotExclamation</t>
+          <t>EmptyPattern</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>= like("!", "[!!]")</t>
+          <t>= like("F", "")</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>ExclamationInSet</t>
+          <t>EmptyText</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>= like("!", "[1-5!]")</t>
+          <t>= like("", "F")</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>SetRepeated</t>
+          <t>EmptyTextAnyCharacters</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>= like("7blabla7", "#[bla]+#")</t>
+          <t>= like("", "*")</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>SetOnce</t>
+          <t>EmptyTextOneCharacter</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>= like("7blabla7", "#[bla]#")</t>
+          <t>= like("", "?")</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>PlainPlus</t>
+          <t>SetWithHyphen</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>= like("+38(099)", "+##(###)")</t>
+          <t>= like("5-5", "[1-5][-4-6][5-9]")</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>SetThenPlus</t>
+          <t>Exclamation</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>= like("BAR+", "[A-Z]++")</t>
+          <t>= like("!", "[!]")</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>NotExclamation</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>= like("foo@bar.com", "?+[@]?+.?+")</t>
+          <t>= like("!", "[!!]")</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>NotEmail</t>
+          <t>ExclamationInSet</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>= like("foo@bar", "?+[@]?+.?+")</t>
+          <t>= like("!", "[1-5!]")</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>LiteralHashStar</t>
+          <t>SetRepeated</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>= like("#*", "[#][*]")</t>
+          <t>= like("7blabla7", "#[bla]+#")</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>NoLetters</t>
+          <t>SetOnce</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>= like("$%&amp;", "*@*")</t>
+          <t>= like("7blabla7", "#[bla]#")</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
+          <t>PlainPlus</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>= like("+38(099)", "+##(###)")</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>SetThenPlus</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>= like("BAR+", "[A-Z]++")</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>= like("foo@bar.com", "?+[@]?+.?+")</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>NotEmail</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>= like("foo@bar", "?+[@]?+.?+")</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>LiteralHashStar</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>= like("#*", "[#][*]")</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>NoLetters</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>= like("$%&amp;", "*@*")</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>SeveralSpaces</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>= like("a   b", "a b")</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="3" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Test LikeEdges LikeEdgesTest</t>
         </is>
       </c>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$OtherCase</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>like("F", "f")</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$OneCharacterOnly</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>like("abc", "?")</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$EmptyBoth</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>like("", "")</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$EmptyPattern</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>like("F", "")</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$EmptyText</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>like("", "F")</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$SetWithHyphen</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>like("5-5", "[1-5][-4-6][5-9]")</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Exclamation</t>
+          <t>_res_.$OtherCase</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>like("!", "[!]")</t>
+          <t>like("F", "f")</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>_res_.$NotExclamation</t>
+          <t>_res_.$OneCharacterOnly</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>like("!", "[!!]")</t>
+          <t>like("abc", "?")</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -3077,12 +3120,12 @@
     <row r="65">
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>_res_.$ExclamationInSet</t>
+          <t>_res_.$EmptyBoth</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>like("!", "[1-5!]")</t>
+          <t>like("", "")</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -3094,29 +3137,29 @@
     <row r="66">
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>_res_.$SetRepeated</t>
+          <t>_res_.$EmptyPattern</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>like("7blabla7", "#[bla]+#")</t>
+          <t>like("F", "")</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>_res_.$SetOnce</t>
+          <t>_res_.$EmptyText</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>like("7blabla7", "#[bla]#")</t>
+          <t>like("", "F")</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -3128,12 +3171,12 @@
     <row r="68">
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>_res_.$PlainPlus</t>
+          <t>_res_.$EmptyTextAnyCharacters</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>like("+38(099)", "+##(###)")</t>
+          <t>like("", "*")</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -3145,29 +3188,29 @@
     <row r="69">
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>_res_.$SetThenPlus</t>
+          <t>_res_.$EmptyTextOneCharacter</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>like("BAR+", "[A-Z]++")</t>
+          <t>like("", "?")</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>_res_.$Email</t>
+          <t>_res_.$SetWithHyphen</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>like("foo@bar.com", "?+[@]?+.?+")</t>
+          <t>like("5-5", "[1-5][-4-6][5-9]")</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -3179,66 +3222,202 @@
     <row r="71">
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>_res_.$NotEmail</t>
+          <t>_res_.$Exclamation</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>like("foo@bar", "?+[@]?+.?+")</t>
+          <t>like("!", "[!]")</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>_res_.$LiteralHashStar</t>
+          <t>_res_.$NotExclamation</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>like("#*", "[#][*]")</t>
+          <t>like("!", "[!!]")</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>_res_.$NoLetters</t>
+          <t>_res_.$ExclamationInSet</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>like("$%&amp;", "*@*")</t>
+          <t>like("!", "[1-5!]")</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="9" t="inlineStr">
         <is>
+          <t>_res_.$SetRepeated</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>like("7blabla7", "#[bla]+#")</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$SetOnce</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>like("7blabla7", "#[bla]#")</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$PlainPlus</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>like("+38(099)", "+##(###)")</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$SetThenPlus</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>like("BAR+", "[A-Z]++")</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$Email</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>like("foo@bar.com", "?+[@]?+.?+")</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$NotEmail</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>like("foo@bar", "?+[@]?+.?+")</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$LiteralHashStar</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>like("#*", "[#][*]")</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$NoLetters</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>like("$%&amp;", "*@*")</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="9" t="inlineStr">
+        <is>
           <t>_res_.$SeveralSpaces</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>like("a   b", "a b")</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -3246,12 +3425,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3834,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I66"/>
+  <dimension ref="A2:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -4171,7 +4350,7 @@
     <row r="31" ht="43.5" customHeight="1">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>concatenate and textJoin write values of any type and skip null values; textJoin also skips empty texts, takes an array as well, and joins without a separator when it is null. textSplit cuts the text at every whole separator and drops empty parts; the separator is plain text, not a pattern. Without a separator, textSplit returns the whole text as one part. format puts values into {0}, {1} and so on.</t>
+          <t>concatenate and textJoin write values of any type and skip null values; textJoin also skips empty texts, takes an array as well, and joins without a separator when it is null. textSplit cuts the text at every whole separator from left to right and drops empty parts, so an empty text has no parts; the separator is plain text, not a pattern. Without a separator, textSplit returns the whole text as one part. format puts values into {0}, {1} and so on.</t>
         </is>
       </c>
     </row>
@@ -4330,304 +4509,419 @@
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TextSplitNoSeparator</t>
+          <t>TextSplitAfterPartialMatch</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>= textSplit(null, "a.b")</t>
+          <t>= textSplit(", ", "a,, b")</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>TextSplitNotPattern</t>
+          <t>TextSplitRepeatedStart</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>= textSplit("[ ]", "a b")</t>
+          <t>= textSplit("ab", "aab")</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TextSplitOnlySeparators</t>
+          <t>TextSplitCutSeparator</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>= length(textSplit(" ", "   "))</t>
+          <t>= textSplit(", ", "a, b,")</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
+          <t>TextSplitNoSeparator</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>= textSplit(null, "a.b")</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>TextSplitNotPattern</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>= textSplit("[ ]", "a b")</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>TextSplitOnlySeparators</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>= length(textSplit(" ", "   "))</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>TextSplitEmptyText</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>= length(textSplit(",", ""))</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>= format("User {1} has policy {0}", "P-1", "Ann")</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Test TextJoins TextJoinsTest</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$Concatenate</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>concatenate("a", 1, 2.5, true)</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>a12.5true</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$ConcatenateOne</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>concatenate("Hello")</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>Hello</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$ConcatenateSkipsNull</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>concatenate("S", '/', null, 5)</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>S/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>_res_.$TextJoin</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>textJoin(", ", "a", null, "b", 3)</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>a, b, 3</t>
-        </is>
-      </c>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextJoinArray</t>
+          <t>_res_.$Concatenate</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>textJoin(", ", new String[] {null, "foo", "", "bar"})</t>
+          <t>concatenate("a", 1, 2.5, true)</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>foo, bar</t>
+          <t>a12.5true</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextJoinNoSeparator</t>
+          <t>_res_.$ConcatenateOne</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>textJoin(null, "a", "b")</t>
+          <t>concatenate("Hello")</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>Hello</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextJoinTypes</t>
+          <t>_res_.$ConcatenateSkipsNull</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>textJoin("; ", 'A', true, 1.5)</t>
+          <t>concatenate("S", '/', null, 5)</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>A; true; 1.5</t>
+          <t>S/5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextJoinNoValues</t>
+          <t>_res_.$TextJoin</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>textJoin(", ", new String[0])</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr"/>
+          <t>textJoin(", ", "a", null, "b", 3)</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>a, b, 3</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplit</t>
+          <t>_res_.$TextJoinArray</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>textSplit(",", "a,b,,c")</t>
+          <t>textJoin(", ", new String[] {null, "foo", "", "bar"})</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>foo, bar</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplitEnds</t>
+          <t>_res_.$TextJoinNoSeparator</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>textSplit(".", "..a..b.")</t>
+          <t>textJoin(null, "a", "b")</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>a, b</t>
+          <t>ab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplitWhole</t>
+          <t>_res_.$TextJoinTypes</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>textSplit("..", "abc..def.xyz")</t>
+          <t>textJoin("; ", 'A', true, 1.5)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>abc, def.xyz</t>
+          <t>A; true; 1.5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplitNoSeparator</t>
+          <t>_res_.$TextJoinNoValues</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>textSplit(null, "a.b")</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>a.b</t>
-        </is>
-      </c>
+          <t>textJoin(", ", new String[0])</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplitNotPattern</t>
+          <t>_res_.$TextSplit</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>textSplit("[ ]", "a b")</t>
+          <t>textSplit(",", "a,b,,c")</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>a b</t>
+          <t>a, b, c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>_res_.$TextSplitOnlySeparators</t>
+          <t>_res_.$TextSplitEnds</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>length(textSplit(" ", "   "))</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>0</v>
+          <t>textSplit(".", "..a..b.")</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>a, b</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="9" t="inlineStr">
         <is>
+          <t>_res_.$TextSplitWhole</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>textSplit("..", "abc..def.xyz")</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>abc, def.xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitAfterPartialMatch</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>textSplit(", ", "a,, b")</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>a\,, b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitRepeatedStart</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>textSplit("ab", "aab")</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitCutSeparator</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>textSplit(", ", "a, b,")</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>a, b\,</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitNoSeparator</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>textSplit(null, "a.b")</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>a.b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitNotPattern</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>textSplit("[ ]", "a b")</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>a b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitOnlySeparators</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>length(textSplit(" ", "   "))</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>_res_.$TextSplitEmptyText</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>length(textSplit(",", ""))</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="9" t="inlineStr">
+        <is>
           <t>_res_.$Format</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>format("User {1} has policy {0}", "P-1", "Ann")</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>User Ann has policy P-1</t>
         </is>
@@ -4639,7 +4933,7 @@
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
